--- a/data/trans_bre/P0901-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 15,39</t>
+          <t>2,51; 14,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 20,52</t>
+          <t>6,99; 20,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 20,92</t>
+          <t>7,42; 20,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 8,46</t>
+          <t>-0,4; 8,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 185,65</t>
+          <t>18,19; 179,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,47; 185,33</t>
+          <t>39,2; 189,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,15; 228,97</t>
+          <t>46,03; 211,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 128,76</t>
+          <t>-4,65; 134,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 12,61</t>
+          <t>4,35; 13,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 12,5</t>
+          <t>3,18; 12,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,47</t>
+          <t>3,92; 12,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,56</t>
+          <t>2,16; 11,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,46; 169,9</t>
+          <t>36,55; 177,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 140,77</t>
+          <t>24,83; 153,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,14; 183,61</t>
+          <t>37,9; 180,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 78,27</t>
+          <t>11,13; 81,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 12,37</t>
+          <t>3,06; 12,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 13,45</t>
+          <t>1,86; 13,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,67</t>
+          <t>-0,85; 8,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 9,01</t>
+          <t>-0,48; 9,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,53; 284,48</t>
+          <t>32,34; 289,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,57; 142,65</t>
+          <t>11,71; 144,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 131,47</t>
+          <t>-9,71; 124,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 73,21</t>
+          <t>-2,78; 74,92</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 15,68</t>
+          <t>6,38; 15,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 23,3</t>
+          <t>10,83; 22,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 22,11</t>
+          <t>9,44; 22,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 8,04</t>
+          <t>-9,58; 7,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,08; 445,63</t>
+          <t>89,0; 459,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,02; 177,87</t>
+          <t>56,41; 169,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,19; 159,71</t>
+          <t>44,03; 155,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 45,69</t>
+          <t>-39,34; 45,28</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,75</t>
+          <t>-1,24; 10,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 19,7</t>
+          <t>5,32; 19,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 10,94</t>
+          <t>-0,64; 11,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,57</t>
+          <t>1,17; 9,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 200,44</t>
+          <t>-13,94; 207,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,14; 218,54</t>
+          <t>30,75; 210,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 186,03</t>
+          <t>-10,15; 215,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,68; 198,97</t>
+          <t>9,46; 192,66</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,17</t>
+          <t>0,86; 12,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 9,35</t>
+          <t>-2,38; 9,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 14,37</t>
+          <t>0,79; 14,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 9,24</t>
+          <t>-0,19; 9,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,32; 184,04</t>
+          <t>3,93; 160,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 84,47</t>
+          <t>-14,42; 93,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 104,72</t>
+          <t>1,88; 112,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 86,97</t>
+          <t>-1,67; 93,28</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,03</t>
+          <t>0,66; 7,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,13</t>
+          <t>2,84; 10,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,17</t>
+          <t>5,86; 14,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 9,96</t>
+          <t>-7,96; 10,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 103,02</t>
+          <t>3,55; 94,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,79; 132,54</t>
+          <t>23,51; 136,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,9; 156,18</t>
+          <t>44,14; 152,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 70,08</t>
+          <t>-46,56; 72,84</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,43</t>
+          <t>3,52; 10,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,14</t>
+          <t>3,4; 11,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,34</t>
+          <t>4,52; 10,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 18,37</t>
+          <t>8,07; 18,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,74; 113,28</t>
+          <t>26,75; 118,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,04; 115,5</t>
+          <t>24,88; 111,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,3; 197,71</t>
+          <t>54,16; 196,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>59,88; 415,03</t>
+          <t>64,35; 379,12</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,85</t>
+          <t>5,77; 8,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,66</t>
+          <t>6,92; 10,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,65</t>
+          <t>7,23; 10,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,29</t>
+          <t>2,96; 9,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57,89; 105,6</t>
+          <t>59,29; 107,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,3; 97,22</t>
+          <t>53,74; 96,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,67; 109,19</t>
+          <t>64,43; 107,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,22; 86,49</t>
+          <t>22,56; 88,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P0901-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P0901-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,67</t>
+          <t>2,75; 15,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 20,6</t>
+          <t>6,84; 20,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 20,62</t>
+          <t>7,24; 20,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 8,15</t>
+          <t>0,41; 8,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 179,46</t>
+          <t>17,58; 174,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,2; 189,49</t>
+          <t>41,57; 190,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,03; 211,15</t>
+          <t>44,63; 212,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 134,39</t>
+          <t>3,54; 139,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 13,3</t>
+          <t>4,55; 12,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,72</t>
+          <t>2,84; 12,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,26</t>
+          <t>3,95; 12,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,88</t>
+          <t>1,08; 10,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,55; 177,01</t>
+          <t>39,18; 169,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,83; 153,79</t>
+          <t>19,03; 146,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,9; 180,13</t>
+          <t>34,62; 188,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 81,95</t>
+          <t>5,46; 67,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,42</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,47</t>
+          <t>3,25; 12,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 13,68</t>
+          <t>1,34; 13,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 8,27</t>
+          <t>-0,97; 8,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 9,17</t>
+          <t>-0,46; 9,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,34; 289,17</t>
+          <t>37,5; 318,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 144,51</t>
+          <t>7,22; 134,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 124,96</t>
+          <t>-11,52; 129,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 74,92</t>
+          <t>-2,89; 78,96</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,86</t>
+          <t>6,9; 16,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 22,63</t>
+          <t>10,98; 23,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 22,13</t>
+          <t>8,69; 22,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 7,81</t>
+          <t>0,0; 12,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,0; 459,57</t>
+          <t>91,81; 482,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,41; 169,59</t>
+          <t>56,18; 165,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,03; 155,5</t>
+          <t>42,52; 157,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 45,28</t>
+          <t>-0,05; 85,5</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,27</t>
+          <t>-1,37; 10,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 19,71</t>
+          <t>5,15; 19,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 11,59</t>
+          <t>-0,9; 10,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,63</t>
+          <t>1,34; 9,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 207,29</t>
+          <t>-17,05; 191,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,75; 210,4</t>
+          <t>27,4; 209,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 215,06</t>
+          <t>-10,94; 189,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 192,66</t>
+          <t>12,8; 203,4</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 12,57</t>
+          <t>2,08; 13,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 9,95</t>
+          <t>-2,34; 9,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 14,82</t>
+          <t>1,08; 15,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 9,3</t>
+          <t>0,18; 9,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,93; 160,17</t>
+          <t>14,8; 181,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 93,79</t>
+          <t>-14,21; 100,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 112,21</t>
+          <t>4,89; 114,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 93,28</t>
+          <t>1,19; 95,0</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>70,26%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,76</t>
+          <t>0,48; 7,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 10,53</t>
+          <t>2,83; 10,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 14,06</t>
+          <t>5,57; 14,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 10,14</t>
+          <t>6,23; 13,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 94,62</t>
+          <t>2,68; 97,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,51; 136,38</t>
+          <t>23,68; 139,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,14; 152,68</t>
+          <t>42,65; 155,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 72,84</t>
+          <t>35,23; 109,53</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11,92</t>
+          <t>8,45</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136,27%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,87</t>
+          <t>3,67; 11,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 11,03</t>
+          <t>3,72; 11,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 10,74</t>
+          <t>4,51; 10,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,07; 18,2</t>
+          <t>5,0; 11,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,75; 118,52</t>
+          <t>28,64; 119,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,88; 111,27</t>
+          <t>26,04; 114,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,16; 196,91</t>
+          <t>55,5; 197,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>64,35; 379,12</t>
+          <t>36,74; 118,43</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,97</t>
+          <t>5,71; 9,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,64</t>
+          <t>7,03; 10,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,61</t>
+          <t>7,12; 10,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,35</t>
+          <t>5,47; 8,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,29; 107,94</t>
+          <t>58,13; 109,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,74; 96,58</t>
+          <t>53,85; 94,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,43; 107,94</t>
+          <t>64,83; 110,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,56; 88,01</t>
+          <t>37,97; 68,44</t>
         </is>
       </c>
     </row>
